--- a/fuzzing-security-testing/BaoCaoATPM/Module_Products_Manage_spec.xlsx
+++ b/fuzzing-security-testing/BaoCaoATPM/Module_Products_Manage_spec.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -479,7 +479,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="160" customHeight="1" s="8">
+    <row r="3" ht="114" customHeight="1" s="8">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>description</t>
@@ -487,7 +487,115 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Đặc tả yêu cầu module PRD của hệ thống bán hàng. API được kiểm thử trên node_harness với datastore trong bộ nhớ; các request có thể chạy đồng thời. Cụm khóa và hàm C/Python/SMT là mô hình kiểm chứng minh họa theo template, gồm lỗi cấy có chủ đích; không phải bằng chứng lỗi bộ nhớ của Node.js. Đây là hợp đồng mong đợi để xây dựng testcase; mức đáp ứng của code được đánh giá riêng, không khẳng định mọi yêu cầu đã triển khai.</t>
+          <t>Đặc tả hợp đồng an toàn module PRD trên hệ thống bán hàng mô phỏng node_harness. Request và code xử lý chạy thực; datastore/dịch vụ là test double. Yêu cầu mong đợi không đồng nghĩa code hiện đã đáp ứng. Giữ đủ 10 sheet và ID testcase; kết quả quan sát lưu riêng trong report/evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="137.6" customHeight="1" s="8">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_chinh</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Blackbox: seed → đột biến → HTTP → oracle. Khảo sát coverage: replay/lân cận → giữ input mở thêm dòng; đây là coverage-guided/greybox. Module này có 5 testcase API được campaign hiện tại thực thi: TC-PRD-1, TC-PRD-2, TC-PRD-3, TC-PRD-5, TC-PRD-4. Oracle hiện chỉ kiểm tra các điều kiện đã cài đặt, không bao phủ mọi yêu cầu mở rộng trong Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="130.4" customHeight="1" s="8">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_bo_tro</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Toàn bộ 5 Excel có 134 testcase; campaign API có 29 testcase/59 kịch bản khi fuzz-cases=8; 105 testcase còn lại được ghi riêng trong excluded_testcases.json, chưa thực thi trong campaign. Race/version, timing, bộ đếm, CTL, mẫu C/Python và mô hình số học được giữ làm đặc tả bổ sung; chưa tuyên bố đã chạy/kiểm chứng lại đầy đủ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" s="8">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>thu_tu_testcase</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>API an toàn đầu vào/quyền/trạng thái → tái hiện và phân loại bằng chứng → mẫu ngoại lệ/bộ nhớ độc lập → concurrency/timing/số học → seed đối chứng. Trong từng nhóm: HIGH, MEDIUM, LOW. ID không thay đổi; kết quả thực tế lưu ở report, không điền vào KetQuaMongDoi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="86.8" customHeight="1" s="8">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>phuong_phap_whitebox</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Module này chưa có concolic/Z3 sinh input trực tiếp. Whitebox --concolic hiện chỉ khảo sát totalAmount của module tạo đơn (TC-ORD-3/4). Cùng có sheet mô hình/SMT không đồng nghĩa đã triển khai concolic cho module này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="124.8" customHeight="1" s="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>pham_vi_mo_hinh</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>MoHinhTrangThai/ThuocTinhAnToan/LoaiTruLanNhau mô tả thuộc tính thiết kế, chưa xác minh CTL trong bộ chạy hiện tại. HamSinhMa chứa thiết kế mẫu minh họa C/Python; KiemTraSoHoc là mô hình số học độc lập theo giả định, không phải path condition của concolic. Không tự đồng nhất mô hình int32 với Number JavaScript.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="131.6" customHeight="1" s="8">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>bang_chung_ket_luan</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 5xx là lỗi phản hồi ứng dụng; timeout là nghi vấn hang. Crash cần log và mã thoát/signal; lỗi bộ nhớ cần chẩn đoán instrumentation phù hợp. SAT/UNSAT/unknown phải lưu công thức và phạm vi; không mặc định SAT, không coi unknown là UNSAT. Không điền kết quả chạy vào KetQuaMongDoi hoặc dùng finding occurrences làm số lỗi gốc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="126" customHeight="1" s="8">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>lenh_chay</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Tại thư mục gốc: python fuzzing-security-testing/fuzzers/run_ch4.py --seed 7 --fuzz-cases 8. Demo có concolic riêng: python fuzzing-security-testing/fuzzers/run_fuzzing.py --iterations 42 --iterations-per-case 8 --max-cases 2 --seed 7 --concolic. Hai chế độ lưu report riêng, không tự thực thi toàn bộ 134 testcase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="104.8" customHeight="1" s="8">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>bao_phu_thuc_thi</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá theo snapshot/hash trong từng report, không tái gán kết quả cũ cho Excel đã sửa. Bộ concolic đối chiếu mô hình với 8 đại diện trong test hồi quy; chiến dịch solver không bắt buộc chạy đủ 8 đại diện. Chưa có sanitizer hoặc bảo đảm coverage toàn hệ thống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bo_sung_runtime</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bổ sung TC-PRD-22 đến TC-PRD-27: discovery, native memory, leak, crash/hang, replay, minimization/dedup. Đây là đặc tả chưa có runner tự động; không thay đổi phạm vi 29 testcase API đã có code. Tổng 134 testcase/105 ngoài campaign theo bộ Excel mới; report/snapshot cũ vẫn thuộc phiên bản 104 testcase, không tái gán số liệu.</t>
         </is>
       </c>
     </row>
@@ -502,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -552,7 +660,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="72" customHeight="1" s="8">
+    <row r="2" ht="81.07142857142858" customHeight="1" s="8">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-1</t>
@@ -565,7 +673,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Tạo/sửa sản phẩm không token</t>
+          <t>Vượt quyền tạo hoặc sửa dữ liệu sản phẩm</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -576,12 +684,13 @@
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>POST /api/products không token
-PUT /api/products/1 không token</t>
+PUT /api/products/1 không token
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ĐÃ XÁC NHẬN THỰC NGHIỆM: cả 2 trả 200 thành công - VI PHẠM</t>
+          <t>HTTP 401/403 khi thiếu token hoặc dùng tài khoản thường cho thao tác quản trị.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -603,7 +712,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Giá sản phẩm âm</t>
+          <t>Giá âm vượt qua ràng buộc miền dữ liệu</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -615,12 +724,13 @@
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. PUT /api/products/1 với body {"price":-500}
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ĐÃ XÁC NHẬN THỰC NGHIỆM: trả về 200 với price âm - VI PHẠM</t>
+          <t>HTTP 400/422 cho giá âm; không coi cập nhật là hợp lệ.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -642,7 +752,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>price sai kiểu dữ liệu</t>
+          <t>Giá sản phẩm sai kiểu gây ngoại lệ xử lý</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -654,12 +764,13 @@
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. PUT /api/products/1 với body {"price":{"a":1}}
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ĐÃ XÁC NHẬN THỰC NGHIỆM: trả về 500 - VI PHẠM</t>
+          <t>HTTP 400/422 cho object thay vì số; không để lỗi chuyển kiểu gây HTTP 500.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -671,661 +782,941 @@
     <row r="5" ht="129.2" customHeight="1" s="8">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>TC-PRD-4</t>
+          <t>TC-PRD-5</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>REQ-PRD-6</t>
+          <t>REQ-PRD-4</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PUT sản phẩm không tồn tại</t>
+          <t>ID trùng gây ghi đè hoặc mơ hồ định danh sản phẩm</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Server đang chạy</t>
+          <t>Đã có sản phẩm id=1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. PUT /api/products/999999 (id không tồn tại)
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>MONG ĐỢI trả về 404 - cần đối chiếu kết quả fuzz thực tế</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="129.2" customHeight="1" s="8">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-4</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>POST với id trùng sản phẩm đã có</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Đã có sản phẩm id=1</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. POST /api/products với body {"id":1,...}
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Từ chối ID trùng hoặc cấp ID mới duy nhất; không tạo hai sản phẩm cùng định danh hoặc ghi đè trái phép.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="246" customHeight="1" s="8">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-21</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FUZZ-21</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra quy trình fuzzing: Khảo sát chiều dài name và buffer mẫu C</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>name API có giới hạn 200 ký tự theo đặc tả; mẫu parse_product_name có buffer B=200 byte, có native driver và AddressSanitizer hoạt động; bắt đầu bằng ASCII để đồng nhất byte/ký tự.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>1. Gửi name ASCII dài 199, 200, 201 ký tự tới API từ trạng thái sạch và lưu response.
+2. Gửi riêng chuỗi ASCII dài B-1, B, B+1 tới driver C với sanitizer, kể cả ký tự kết thúc chuỗi.
+3. Lưu từng input, lệnh biên dịch, stderr, exit code và stack trace.
+4. Chạy lại điểm lỗi và đối chứng ngắn; thử UTF-8 riêng, ghi cả byte và số ký tự.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Có hai bảng kết quả riêng API và native C. Với strcpy vào buffer B, chuỗi B ký tự còn cần byte kết thúc; chỉ xác nhận overflow bằng sanitizer ở binary C. API trả 500 hoặc từ chối name không đủ để kết luận lỗi bộ nhớ. Không có công cụ thì chưa đánh giá.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="326" customHeight="1" s="8">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FIX-parse_product_name</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: parse_product_name (buffer-overflow)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C parse_product_name, lỗi cấy buffer-overflow; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi parse_product_name, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy chuỗi ASCII dài B-1, B, B+1 với B=200 byte và đối chứng ngắn.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán buffer-overflow; mẫu lỗi cấy phải có chẩn đoán buffer-overflow tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="342" customHeight="1" s="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-10</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FIX-write_product_update_log</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: write_product_update_log (memory-leak)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C write_product_update_log, lỗi cấy memory-leak; có driver gọi hàm, compiler và LeakSanitizer hoặc công cụ kiểm tra leak tương đương hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi write_product_update_log, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán memory-leak; mẫu lỗi cấy phải có chẩn đoán memory-leak tại hàm mục tiêu từ LeakSanitizer hoặc công cụ phát hiện leak tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="310" customHeight="1" s="8">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-11</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FIX-close_product_edit_session</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: close_product_edit_session (double-free)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C close_product_edit_session, lỗi cấy double-free; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi close_product_edit_session, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán double-free; mẫu lỗi cấy phải có chẩn đoán double-free tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="310" customHeight="1" s="8">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-12</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FIX-release_product_list_cache</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Hàm sinh mã C: release_product_list_cache (use-after-free)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu C release_product_list_cache, lỗi cấy use-after-free; có driver gọi hàm, compiler và AddressSanitizer hoạt động. Phạm vi native fixture, không phải API Node.js.
+Chỉ chạy trên hàm C minh họa độc lập; cần compiler và instrumentation phù hợp. Không phải đường thực thi native đã xác nhận của API Node.js.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1. Sinh mã C và chạy kiểm tra tĩnh như testcase gốc.
+2. Tạo driver gọi release_product_list_cache, biên dịch -g -O0 và instrumentation phù hợp; kiểm tra đối chứng công cụ.
+3. Chạy đường thực thi hàm một lần trên mỗi tiến trình mới; có đối chứng đã sửa tương ứng.
+4. Lưu input, binary/source hash, stderr, exit code/signal và vị trí chẩn đoán.
+5. Tái hiện từ tiến trình sạch; chạy đối chứng an toàn cùng input.
+Chạy cả mẫu lỗi cấy và đối chứng an toàn trên cùng input; lưu input, build flags, stderr, mã thoát và vị trí lỗi; lặp lại input gây lỗi.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng an toàn không có chẩn đoán use-after-free; mẫu lỗi cấy phải có chẩn đoán use-after-free tại hàm mục tiêu từ AddressSanitizer hoặc công cụ phát hiện lỗi bộ nhớ tương đương. Mẫu lỗi bị phát hiện là xác nhận đối chứng công cụ, không phải ứng dụng đã an toàn. Thiếu công cụ/bằng chứng: chưa xác minh. Không dùng HTTP 500 làm bằng chứng; leak không bắt buộc làm tiến trình crash.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="129.2" customHeight="1" s="8">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-8</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FIX-out_of_stock_ratio</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hàm Python: out_of_stock_ratio chia cho 0</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Đã sinh mã Python Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
+2. Chạy blackbox_fuzz() với initial_stock=0
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>MONG ĐỢI từ chối hoặc tự động cấp id khác; cần kiểm chứng code hiện tại có ghi đè hay không</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Mẫu lỗi cấy phát sinh ZeroDivisionError với input chia cho 0; lưu traceback, input và cách gọi. Đối chứng an toàn xử lý trường hợp này có kiểm soát. Ngoại lệ Python chưa chứng minh crash server hoặc lỗi bộ nhớ native; thiếu thực thi thì chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="113.8" customHeight="1" s="8">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="12" ht="113.8" customHeight="1" s="8">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-1, NFR-PRD-4, REQ-CONC-PRD-1</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>2 request PUT đồng thời cùng 1 sản phẩm (race tồn kho)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Đã có sản phẩm id=1, stock=10</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>1. Seed đối tượng __v=0; dùng actor có quyền theo kịch bản.
 2. Gửi đồng thời hai PUT dữ liệu khác nhau, cùng __v=0.
 3. Đọc phản hồi, version và dữ liệu cuối.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Một HTTP 200 và một HTTP 409; __v cuối bằng 1; dữ liệu cuối khớp request thành công.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="113.8" customHeight="1" s="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-7</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-FIX-parse_product_name</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: parse_product_name (buffer-overflow)</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source()
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện CWE-120</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="129.2" customHeight="1" s="8">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-8</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-FIX-out_of_stock_ratio</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Hàm Python: out_of_stock_ratio chia cho 0</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã Python Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy blackbox_fuzz() với initial_stock=0
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Tìm được crash ZeroDivisionError (CWE-248)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="144.6" customHeight="1" s="8">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="144.6" customHeight="1" s="8">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-17</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>REQ-CONC-PRD-1</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Version cũ sau cập nhật thành công</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Tài nguyên v=0, actor được phép sửa. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>1. PUT /api/products/{product_id} với __v=0; gửi PUT lần hai vẫn __v=0; đọc lại dữ liệu.
+2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
+Dữ liệu thử: {"stock":11,"__v":0}</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Lần đầu 200/v=1; lần hai 409; dữ liệu và version không đổi sau lần bị từ chối.</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="160" customHeight="1" s="8">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-18</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REQ-CONC-PRD-1</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Version sai kiểu hoặc ngoài miền</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Tài nguyên tồn tại trong harness. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>1. PUT /api/products/{product_id} với lần lượt các giá trị __v; kiểm tra dữ liệu sau mỗi lần.
+2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
+Dữ liệu thử: __v: -1, 0.5, "0", null, true, {}, []</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Mỗi request trả 400; dữ liệu/version không thay đổi.</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="144.6" customHeight="1" s="8">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-19</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>REQ-CONC-PRD-1</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Cập nhật tuần tự với version mới nhất</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Tài nguyên v=0, actor được phép sửa. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>1. PUT __v=0; đọc __v=1; PUT giá trị khác với __v=1; đọc lại.
+2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
+Dữ liệu thử: [{"stock":11,"__v":0},{"stock":12,"__v":1}]</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Cả hai trả 200; version cuối bằng 2; dữ liệu khớp lần thứ hai.</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="129.2" customHeight="1" s="8">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-20</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>CON-PRD-5</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Client cũ không gửi version</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Tài nguyên tồn tại trong harness; giao thức tương thích hiện tại. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>1. PUT /api/products/{product_id} với dữ liệu hợp lệ, không có trường __v; đọc lại.
+2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
+Dữ liệu thử: {"stock":11}</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Theo hành vi tương thích hiện tại: 200 và version tăng 1. Không kết luận chống stale-write cho client bỏ version.</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="144.6" customHeight="1" s="8">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-9</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-SMT-total_stock_movement_counter</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: total_stock_movement_counter</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="129.2" customHeight="1" s="8">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-FIX-write_product_update_log</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: write_product_update_log (memory-leak)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm write_product_update_log Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện thiếu free() tương ứng với malloc() (memory-leak, CWE-401)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="129.2" customHeight="1" s="8">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-11</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-FIX-close_product_edit_session</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: close_product_edit_session (double-free)</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm close_product_edit_session Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện free() được gọi 2 lần trên cùng 1 con trỏ (double-free, CWE-415)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="129.2" customHeight="1" s="8">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-12</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>REQ-PRD-FIX-release_product_list_cache</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Hàm sinh mã C: release_product_list_cache (use-after-free)</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Đã sinh mã C cho hàm release_product_list_cache Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
-2. Chạy check_c_source() trên mã sinh ra
-3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Phát hiện vùng nhớ được truy cập SAU khi đã free() (use-after-free, CWE-416)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="175.4" customHeight="1" s="8">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="18" ht="175.4" customHeight="1" s="8">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-13</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-SMT-daily_product_update_counter</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: daily_product_update_counter</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'daily_product_update_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'daily_product_update_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="175.4" customHeight="1" s="8">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="19" ht="175.4" customHeight="1" s="8">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-14</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-SMT-concurrent_stock_update_counter</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: concurrent_stock_update_counter</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'concurrent_stock_update_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'concurrent_stock_update_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="175.4" customHeight="1" s="8">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="20" ht="175.4" customHeight="1" s="8">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-15</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-SMT-total_product_create_counter</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: total_product_create_counter</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'total_product_create_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'total_product_create_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="175.4" customHeight="1" s="8">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="21" ht="175.4" customHeight="1" s="8">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>TC-PRD-16</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>REQ-PRD-SMT-out_of_stock_event_counter</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Kiểm tra tràn số: out_of_stock_event_counter</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Đã khai báo biến SMT tương ứng cho dòng 'out_of_stock_event_counter' Phạm vi mô hình minh họa theo template, không phải lỗi API Node.js.</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
 2. Chạy check_int32_overflow() bằng Z3 trên BieuThucTran của dòng 'out_of_stock_event_counter'
 3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả SAT (vẫn có thể tràn số nếu chỉ dùng kiểu dữ liệu hẹp như giả định nghiệp vụ)</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá công thức theo đúng miền, signedness và độ rộng bit trong sheet KiemTraSoHoc. Nếu SAT, lưu giá trị chứng minh và phép toán gây vượt miền; nếu UNSAT, lưu giả định và phạm vi đã kiểm tra. Không mặc định SAT và không suy ra tràn số runtime Node.js từ mô hình số nguyên hữu hạn. Chưa chạy solver: chưa xác minh.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="144.6" customHeight="1" s="8">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-17</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>REQ-CONC-PRD-1</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Version cũ sau cập nhật thành công</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Tài nguyên v=0, actor được phép sửa. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>1. PUT /api/products/{product_id} với __v=0; gửi PUT lần hai vẫn __v=0; đọc lại dữ liệu.
-2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: {"stock":11,"__v":0}</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Lần đầu 200/v=1; lần hai 409; dữ liệu và version không đổi sau lần bị từ chối.</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="160" customHeight="1" s="8">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-18</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>REQ-CONC-PRD-1</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Version sai kiểu hoặc ngoài miền</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Tài nguyên tồn tại trong harness. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>1. PUT /api/products/{product_id} với lần lượt các giá trị __v; kiểm tra dữ liệu sau mỗi lần.
-2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: __v: -1, 0.5, "0", null, true, {}, []</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Mỗi request trả 400; dữ liệu/version không thay đổi.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="144.6" customHeight="1" s="8">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-19</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>REQ-CONC-PRD-1</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Cập nhật tuần tự với version mới nhất</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Tài nguyên v=0, actor được phép sửa. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>1. PUT __v=0; đọc __v=1; PUT giá trị khác với __v=1; đọc lại.
-2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: [{"stock":11,"__v":0},{"stock":12,"__v":1}]</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Cả hai trả 200; version cuối bằng 2; dữ liệu khớp lần thứ hai.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="129.2" customHeight="1" s="8">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>TC-PRD-20</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CON-PRD-5</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Client cũ không gửi version</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Tài nguyên tồn tại trong harness; giao thức tương thích hiện tại. Phạm vi: harness mô phỏng; testcase mới chưa có kịch bản thực thi tự động.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>1. PUT /api/products/{product_id} với dữ liệu hợp lệ, không có trường __v; đọc lại.
-2. Thu thập response và dữ liệu cuối để đối chiếu kết quả mong đợi.
-Dữ liệu thử: {"stock":11}</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Theo hành vi tương thích hiện tại: 200 và version tăng 1. Không kết luận chống stale-write cho client bỏ version.</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+    <row r="22" ht="129.2" customHeight="1" s="8">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-4</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-6</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Đối chứng lỗi truy cập sản phẩm không tồn tại</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Server đang chạy</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>1. Chuẩn bị trạng thái và dữ liệu như điều kiện tiên quyết.
+2. PUT /api/products/999999 (id không tồn tại)
+3. Thu thập phản hồi/trạng thái cuối và đối chiếu kết quả mong đợi.
+Lưu seed, input thực tế, ngữ cảnh xác thực/trạng thái, response và thời gian. Chỉ kết luận crash khi có mã thoát/signal và log tiến trình; timeout là nghi vấn hang.</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 404 có kiểm soát; không báo lỗi tiến trình khi tài nguyên không tồn tại.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Khám phá lỗi runtime chưa biết bằng seed và mutation có ngân sách</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có runner cô lập và giới hạn thời gian mỗi lượt, số lượt, kích thước input, CPU/RAM. Có seed đối chứng chạy được.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Reset trạng thái, chạy seed đối chứng và xác nhận tới target. 2. Đột biến name UTF-8, ID, price, stock, variants; độ dài byte, số phần tử và kiểu dữ liệu; trộn mutation có cấu trúc và byte-level khi parser/driver hỗ trợ. 3. Chốt random seed=7, ngân sách 1000 input mới, tối đa 64 KiB/input, timeout mỗi target=2 giây sau setup; điều chỉnh có ghi lý do trước chạy nếu đối chứng không đáp ứng. 4. Chạy nhiều random seed độc lập; lưu toàn bộ input có triệu chứng và corpus mở coverage nếu có. Không hardcode input lỗi duy nhất. 5. Reset từng lượt hoặc lưu đầy đủ prefix trạng thái với target stateful. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Seed đối chứng tới đúng target. Lưu input mới và triệu chứng thực đo; không có lỗi trong ngân sách chỉ ghi NOT_FOUND_WITHIN_BUDGET, không chứng minh an toàn. HTTP 5xx là lỗi ứng dụng, không tự là crash/bộ nhớ. Thiếu runner/giám sát: NOT_IMPLEMENTED hoặc INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-23</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-MEMORY</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Khám phá truy cập bộ nhớ sai bằng target native instrumented</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có mã C/C++ hoặc native dependency thực có driver nhận input; compiler và ASan (hoặc công cụ tương đương) hoạt động. Nếu chỉ có API JS thì chưa đáp ứng điều kiện này.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Xác định target native và đường gọi; nếu dùng hàm HamSinhMa phải ghi là fixture độc lập. 2. Build có debug symbols và instrumentation; chạy đối chứng an toàn và mẫu lỗi biết trước để xác nhận công cụ. 3. Dùng seed hợp lệ rồi fuzz name UTF-8, ID, price, stock, variants; độ dài byte, số phần tử và kiểu dữ liệu; thử B-1/B/B+1 theo BYTE, tính cả NUL khi dùng chuỗi C. 4. Thu chẩn đoán out-of-bounds/use-after-free/double-free, stack và allocation/free stack nếu công cụ cung cấp. 5. Replay input từ tiến trình sạch ba lần và đối chiếu mẫu đã sửa. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ xác nhận loại lỗi khi diagnostic chỉ vào thao tác bộ nhớ sai trong binary mục tiêu. Crash đơn thuần không xác định loại lỗi bộ nhớ; ASan không bảo đảm phát hiện mọi lỗi. Đối chứng lỗi cấy được phát hiện chỉ xác nhận công cụ, không phải phát hiện production. Thiếu instrumentation/driver: chưa đánh giá.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-24</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-LEAK</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Kiểm tra rò rỉ cấp phát và tăng trưởng bộ nhớ qua vòng đời thao tác</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có driver native với LSan/công cụ leak tương đương hoặc profiler heap cho Node; có warmup, đối chứng an toàn và cấu hình tài nguyên cố định.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Làm nóng bằng 100 thao tác hợp lệ. 2. Reset và chạy ba batch độc lập, mỗi batch 1000 thao tác từ seed/mutation có giới hạn. 3. Với native, thu leak report và allocation stack khi kết thúc bình thường; không chỉ kill timeout. 4. Với Node, chụp heap trước/sau cùng điều kiện GC, truy vết retaining path và ownership; tách dữ liệu nghiệp vụ cố ý giữ trong datastore khỏi rò rỉ. 5. So sánh đối chứng đã giải phóng tài nguyên; ghi RSS/heap theo thời gian. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Native leak cần chẩn đoán allocation không được thu hồi; retention Node cần chứng minh đối tượng hết vòng đời vẫn bị giữ ngoài thiết kế. RAM/RSS tăng, GC trễ hoặc Map lưu thêm đơn hợp lệ chưa đủ kết luận leak. OOM phải phân loại riêng và chưa tự chứng minh leak; thiếu công cụ: INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-25</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-CRASH_HANG</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Giám sát và phân biệt crash, timeout, hang, OOM và lỗi ứng dụng</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có supervisor quan sát đúng target PID, handshake READY, health probe và fixture nhanh/crash/chờ độc lập; không dùng tiến trình production.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Chạy đối chứng nhanh, HTTP 500 còn sống, kết thúc bình thường, crash có chủ đích và fixture chờ. 2. Bắt đầu timeout 2 giây sau READY; tách thời gian startup/setup. 3. Khi quá hạn, ghi target còn sống, probe/liveness và log trước khi cleanup. 4. Phân biệt target tự dừng với supervisor terminate/kill và hết giới hạn tài nguyên. 5. Replay cùng input/prefix ba tiến trình sạch; loại trừ sai cổng, kết nối, setup và tải máy. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>HTTP 500 còn sống=APPLICATION_HTTP_ERROR; quá hạn=SUSPECTED_HANG, chỉ xác nhận hang khi lặp có kiểm soát và có quan sát tiến trình. Crash cần bằng chứng target dừng bất thường, không do cleanup; exit khác 0 do validation/sanitizer phải có phân loại nguyên nhân. OOM cần diagnostic/giới hạn tài nguyên, không tự là memory corruption. Đối chứng không được phân loại nhầm; thiếu bằng chứng=INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-26</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-REPLAY</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Tái hiện input runtime với trạng thái ban đầu và prefix đầy đủ</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có artifact của input phát hiện trong lượt khám phá; có snapshot/reset và build tương ứng. Không có finding thì ghi NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Đọc artifact, khôi phục build/config, dữ liệu và actor; ánh xạ ID/token test mới theo vai trò. 2. Chạy seed đối chứng. 3. Replay input độc lập và replay cùng prefix đã ghi, mỗi chế độ ba lần từ tiến trình sạch. 4. So sánh diagnostic, stack chuẩn hóa, exit/liveness và trạng thái sau cùng; ghi tỷ lệ tái hiện. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ ghi tái hiện xác nhận khi cùng loại triệu chứng và bằng chứng mục tiêu lặp lại; lỗi setup/version không được thay cho lỗi gốc. Không tái hiện phải giữ artifact và ghi NOT_REPRODUCED/STATE_DEPENDENT/INCONCLUSIVE theo bằng chứng; không tự bác bỏ phát hiện.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TC-PRD-27</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-MINIMIZE</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Thu nhỏ input và nhóm phát hiện runtime theo chữ ký bằng chứng</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Luồng mục tiêu: quyền quản trị → ID → name/giá/variants/tồn kho → lưu → cache. Trạng thái sạch: seed_product_valid.json; actor admin, catalog và __v cố định, phân biệt tạo mới/cập nhật. Có finding đã replay; có oracle giữ nguyên loại lỗi/stack mục tiêu, reset sạch và ngân sách tối đa 200 phép thử giảm; giữ artifact gốc bất biến.</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Giảm trường, độ dài byte, phần tử mảng hoặc prefix từng bước. 2. Mỗi ứng viên chạy sạch, giữ lại chỉ khi còn cùng diagnostic/stack mục tiêu. 3. Dừng khi hết ngân sách hoặc không giảm thêm, replay bản nhỏ ba lần. 4. Nhóm theo target/build, loại lỗi và stack chuẩn hóa; loại địa chỉ ngẫu nhiên, giữ function/source location. 5. Liên kết input gốc, input giảm và lịch sử thử; hang dùng chữ ký liveness/prefix riêng. Lưu seed/corpus hash, random seed, input thực tế, chuỗi setup, actor/quyền, phiên bản nguồn/binary/runtime, build flags, thời gian, PID, stdout/stderr, exit code/signal và trạng thái trước/sau; che token/password/secret. </t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Bản giảm phải giữ triệu chứng gốc, không chuyển từ lỗi bộ nhớ sang validation/setup. Chỉ gọi là đã giảm trong ngân sách, không khẳng định nhỏ nhất toàn cục. Nhóm chữ ký là ứng viên cùng nguyên nhân, không chứng minh số lỗi gốc; số occurrences báo cáo riêng. Không có finding=NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1342,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -1809,6 +2200,160 @@
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1" s="8">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>REQ-PRD-FUZZ-21</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Phải phân biệt giới hạn độ dài API với kích thước buffer C; khảo sát lân cận không tự chứng minh memory corruption trong API Node.js.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>functional</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-DISCOVERY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Khám phá lỗi runtime chưa biết bằng seed và mutation có ngân sách. Seed đối chứng tới đúng target. Lưu input mới và triệu chứng thực đo; không có lỗi trong ngân sách chỉ ghi NOT_FOUND_WITHIN_BUDGET, không chứng minh an toàn. HTTP 5xx là lỗi ứng dụng, không tự là crash/bộ nhớ. Thiếu runner/giám sát: NOT_IMPLEMENTED hoặc INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-MEMORY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Khám phá truy cập bộ nhớ sai bằng target native instrumented. Chỉ xác nhận loại lỗi khi diagnostic chỉ vào thao tác bộ nhớ sai trong binary mục tiêu. Crash đơn thuần không xác định loại lỗi bộ nhớ; ASan không bảo đảm phát hiện mọi lỗi. Đối chứng lỗi cấy được phát hiện chỉ xác nhận công cụ, không phải phát hiện production. Thiếu instrumentation/driver: chưa đánh giá.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-LEAK</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Kiểm tra rò rỉ cấp phát và tăng trưởng bộ nhớ qua vòng đời thao tác. Native leak cần chẩn đoán allocation không được thu hồi; retention Node cần chứng minh đối tượng hết vòng đời vẫn bị giữ ngoài thiết kế. RAM/RSS tăng, GC trễ hoặc Map lưu thêm đơn hợp lệ chưa đủ kết luận leak. OOM phải phân loại riêng và chưa tự chứng minh leak; thiếu công cụ: INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-CRASH_HANG</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Giám sát và phân biệt crash, timeout, hang, OOM và lỗi ứng dụng. HTTP 500 còn sống=APPLICATION_HTTP_ERROR; quá hạn=SUSPECTED_HANG, chỉ xác nhận hang khi lặp có kiểm soát và có quan sát tiến trình. Crash cần bằng chứng target dừng bất thường, không do cleanup; exit khác 0 do validation/sanitizer phải có phân loại nguyên nhân. OOM cần diagnostic/giới hạn tài nguyên, không tự là memory corruption. Đối chứng không được phân loại nhầm; thiếu bằng chứng=INCONCLUSIVE.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-REPLAY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Tái hiện input runtime với trạng thái ban đầu và prefix đầy đủ. Chỉ ghi tái hiện xác nhận khi cùng loại triệu chứng và bằng chứng mục tiêu lặp lại; lỗi setup/version không được thay cho lỗi gốc. Không tái hiện phải giữ artifact và ghi NOT_REPRODUCED/STATE_DEPENDENT/INCONCLUSIVE theo bằng chứng; không tự bác bỏ phát hiện.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>REQ-PRD-RUNTIME-MINIMIZE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Đặc tả mới, chưa được bộ chạy hiện tại tự động thực thi; không gán PASS/FAIL khi chưa có bằng chứng. API Node.js, native dependency thực và mẫu C lỗi cấy phải báo cáo tách biệt. Thu nhỏ input và nhóm phát hiện runtime theo chữ ký bằng chứng. Bản giảm phải giữ triệu chứng gốc, không chuyển từ lỗi bộ nhớ sang validation/setup. Chỉ gọi là đã giảm trong ngân sách, không khẳng định nhỏ nhất toàn cục. Nhóm chữ ký là ứng viên cùng nguyên nhân, không chứng minh số lỗi gốc; số occurrences báo cáo riêng. Không có finding=NO_CANDIDATE.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
